--- a/results/log_pv_inst_fit/log_pv_inst_fit_densities_adensity_estimates.xlsx
+++ b/results/log_pv_inst_fit/log_pv_inst_fit_densities_adensity_estimates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,41 +462,11 @@
           <t>densities-ML_ErrorFE-queen-Running ML_ErrorFE:queen for log_pv_inst_fit ~ (densities): adensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>densities-PooledOLS-inverse_distance-Running PooledOLS:inverse_distance for log_pv_inst_fit ~ (densities): adensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>densities-PooledOLS-k_nearest-Running PooledOLS:k_nearest for log_pv_inst_fit ~ (densities): adensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>densities-PooledOLS-queen-Running PooledOLS:queen for log_pv_inst_fit ~ (densities): adensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>densities-PanelRE-inverse_distance-Running PanelRE:inverse_distance for log_pv_inst_fit ~ (densities): adensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>densities-PanelRE-k_nearest-Running PanelRE:k_nearest for log_pv_inst_fit ~ (densities): adensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>densities-PanelRE-queen-Running PanelRE:queen for log_pv_inst_fit ~ (densities): adensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>adensity</t>
+          <t>D(Firm assets)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -542,43 +512,13 @@
       <c r="J2" t="inlineStr">
         <is>
           <t>0.000*</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>-0.000</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-0.000</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>-0.000</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>log_income</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -624,43 +564,13 @@
       <c r="J3" t="inlineStr">
         <is>
           <t>0.236**</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>-1.246***</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-1.246***</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>-1.246***</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>1.959***</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>1.959***</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>1.959***</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>log_hholds</t>
+          <t>Households</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -706,43 +616,13 @@
       <c r="J4" t="inlineStr">
         <is>
           <t>0.003*</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.006</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>0.006</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0.006</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>log_sunny_hours</t>
+          <t>Sunny hours</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -788,126 +668,96 @@
       <c r="J5" t="inlineStr">
         <is>
           <t>0.185***</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0.433**</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>0.433**</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0.433**</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>-0.170***</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>-0.170***</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>-0.170***</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>W_adensity</t>
+          <t>Spatial term, ρ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.000</t>
+          <t>0.875***</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.000*</t>
+          <t>0.705***</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.000*</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+          <t>0.595***</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.962***</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.785***</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.691***</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>W_log_income</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>0.558***</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0.731***</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0.931***</t>
-        </is>
-      </c>
+          <t>Spatial term, λ</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.973***</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.891***</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.841***</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>W_log_hholds</t>
+          <t>W(D(Firm assets))</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.058**</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.009*</t>
+          <t>-0.000*</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-0.008***</t>
+          <t>-0.000*</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -916,32 +766,26 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>W_log_sunny_hours</t>
+          <t>W(Income)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-0.286***</t>
+          <t>0.558***</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.327***</t>
+          <t>0.731***</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-0.321***</t>
+          <t>0.931***</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -950,891 +794,320 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>W_log_pv_inst_fit</t>
+          <t>W(Households)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.875***</t>
+          <t>-0.058**</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.705***</t>
+          <t>-0.009*</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.595***</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.962***</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0.785***</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0.691***</t>
-        </is>
-      </c>
+          <t>-0.008***</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>r2</t>
+          <t>W(Sunny hours)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.850</t>
+          <t>-0.286***</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.828</t>
+          <t>-0.327***</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.812</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0.849</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0.824</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0.804</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.007</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.273</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0.383</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.114</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>0.114</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>0.114</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0.111</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0.111</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>0.111</t>
-        </is>
-      </c>
+          <t>-0.321***</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>aic</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-9799.598</t>
+          <t>0.850</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-9382.512</t>
+          <t>0.828</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-9172.027</t>
+          <t>0.812</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-9768.423</t>
+          <t>0.849</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-9281.337</t>
+          <t>0.824</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-9012.901</t>
+          <t>0.804</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-9782.344</t>
+          <t>0.007</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-9192.010</t>
+          <t>0.273</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-8819.634</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>1483.993</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>1483.993</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>1483.993</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2776.043</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2776.043</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2776.043</t>
+          <t>0.383</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>schwarz</t>
+          <t>AIC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>-9748.854</t>
+          <t>-9799.598</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-9331.768</t>
+          <t>-9382.512</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-9121.284</t>
+          <t>-9172.027</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-9740.232</t>
+          <t>-9768.423</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-9253.146</t>
+          <t>-9281.337</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-8984.710</t>
+          <t>-9012.901</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-9759.791</t>
+          <t>-9782.344</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-9169.457</t>
+          <t>-9192.010</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-8797.082</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>1512.183</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>1512.183</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>1512.183</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2804.234</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2804.234</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2804.234</t>
+          <t>-8819.634</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>llr</t>
+          <t>BIC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4908.799</t>
+          <t>-9748.854</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4700.256</t>
+          <t>-9331.768</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4595.014</t>
+          <t>-9121.284</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4889.212</t>
+          <t>-9740.232</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>4645.669</t>
+          <t>-9253.146</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4511.450</t>
+          <t>-8984.710</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4895.172</t>
+          <t>-9759.791</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4600.005</t>
+          <t>-9169.457</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>4413.817</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>-736.996</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>-736.996</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>-736.996</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>-1383.022</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>-1383.022</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>-1383.022</t>
+          <t>-8797.082</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>n_obs</t>
+          <t>Log-Likelihood</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4908.799</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4700.256</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4595.014</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4889.212</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4645.669</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4511.450</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4895.172</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4600.005</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2076</t>
+          <t>4413.817</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>tests</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        Test    Statistic  df  p-value
-0       LM Marginal RE (LM1)    67.183115   1      0.0
-1  LM Marginal Spatial (LM2)    18.289893   1      0.0
-2             LM Joint (LMJ)  4848.091091   2      0.0</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        Test    Statistic  df       p-value
-0       LM Marginal RE (LM1)    67.183115   1  0.000000e+00
-1  LM Marginal Spatial (LM2)     8.112098   1  2.220446e-16
-2             LM Joint (LMJ)  4579.377046   2  0.000000e+00</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        Test    Statistic  df       p-value
-0       LM Marginal RE (LM1)    67.183115   1  0.000000e+00
-1  LM Marginal Spatial (LM2)     7.969853   1  7.771561e-16
-2             LM Joint (LMJ)  4577.089476   2  0.000000e+00</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                         Test   Statistic df p-value
-0      LM Conditional Spatial  155.324018  1     0.0
-1  Hausman Specification Test -141.133206  4     1.0</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                         Test   Statistic df p-value
-0      LM Conditional Spatial   38.774721  1     0.0
-1  Hausman Specification Test -141.133206  4     1.0</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                         Test   Statistic df p-value
-0      LM Conditional Spatial   26.039729  1     0.0
-1  Hausman Specification Test -141.133206  4     1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>outputs</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           var_names coefficients   std_err    zt_stat      prob
-0           adensity     0.000005  0.000002   2.293787  0.021803
-1         log_income     -0.06154  0.073398  -0.838448  0.401779
-2         log_hholds     0.000808  0.001193   0.677265  0.498238
-3    log_sunny_hours     0.161963  0.034455   4.700684  0.000003
-4         W_adensity    -0.000067  0.000056  -1.181495  0.237406
-5       W_log_income     0.557641  0.140212   3.977126   0.00007
-6       W_log_hholds    -0.057567  0.018732  -3.073156  0.002118
-7  W_log_sunny_hours    -0.286401  0.055019  -5.205527       0.0
-8  W_log_pv_inst_fit     0.874769  0.029987  29.171871       0.0</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           var_names coefficients   std_err   zt_stat      prob
-0           adensity     0.000004  0.000002  1.977798  0.047952
-1         log_income     0.000206  0.075135  0.002738  0.997815
-2         log_hholds     0.001038  0.001278  0.812056   0.41676
-3    log_sunny_hours      0.14611  0.035002  4.174302   0.00003
-4         W_adensity    -0.000015  0.000007 -2.092018  0.036437
-5       W_log_income     0.730655  0.092322  7.914179       0.0
-6       W_log_hholds    -0.009365  0.003777 -2.479576  0.013154
-7  W_log_sunny_hours    -0.326953   0.04605 -7.099918       0.0
-8  W_log_pv_inst_fit     0.705494  0.020944  33.68417       0.0</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           var_names coefficients   std_err    zt_stat      prob
-0           adensity     0.000004  0.000002    1.64663  0.099634
-1         log_income     0.035692  0.075157   0.474896  0.634861
-2         log_hholds     0.001132  0.001334   0.848914  0.395929
-3    log_sunny_hours     0.111162  0.035781   3.106781  0.001891
-4         W_adensity    -0.000009  0.000004   -2.25393  0.024201
-5       W_log_income     0.930784  0.086188  10.799521       0.0
-6       W_log_hholds    -0.008433  0.002186   -3.85804  0.000114
-7  W_log_sunny_hours    -0.320602  0.044539  -7.198201       0.0
-8  W_log_pv_inst_fit     0.594933  0.021399  27.802226       0.0</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           var_names coefficients   std_err    zt_stat      prob
-0           adensity     0.000005  0.000002   2.254426  0.024169
-1         log_income     0.033044  0.025802   1.280638  0.200321
-2         log_hholds     0.000994  0.001194   0.832241  0.405273
-3    log_sunny_hours     0.067822  0.025275   2.683336  0.007289
-4  W_log_pv_inst_fit     0.961871   0.00982  97.948469       0.0</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           var_names coefficients   std_err    zt_stat      prob
-0           adensity     0.000004  0.000002   1.894014  0.058223
-1         log_income     0.410693  0.037228  11.031768       0.0
-2         log_hholds     0.001581  0.001291   1.224865  0.220626
-3    log_sunny_hours     0.022237  0.025343   0.877447  0.380244
-4  W_log_pv_inst_fit     0.784866   0.01583  49.580254       0.0</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           var_names coefficients   std_err    zt_stat      prob
-0           adensity     0.000004  0.000002   1.653034  0.098324
-1         log_income     0.607145  0.041158  14.751579       0.0
-2         log_hholds     0.001684  0.001362   1.236725  0.216189
-3    log_sunny_hours     0.001593  0.026674   0.059722  0.952377
-4  W_log_pv_inst_fit      0.69149  0.017216  40.164491       0.0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err     zt_stat      prob
-0         adensity     0.000005  0.000002    2.358043  0.018372
-1       log_income    -0.044206   0.07318   -0.604073  0.545795
-2       log_hholds     0.001156  0.001188    0.972924  0.330591
-3  log_sunny_hours     0.162164  0.034504    4.699877  0.000003
-4           lambda     0.972894  0.007563  128.639901       0.0</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err   zt_stat      prob
-0         adensity     0.000005  0.000002  2.478623  0.013189
-1       log_income     0.149868  0.072004  2.081383  0.037399
-2       log_hholds     0.002246  0.001219  1.841945  0.065483
-3  log_sunny_hours     0.186261  0.035241  5.285305       0.0
-4           lambda     0.891399  0.010009  89.05929       0.0</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         adensity     0.000005  0.000002   2.232146  0.025605
-1       log_income      0.23642  0.071868   3.289658  0.001003
-2       log_hholds     0.002829  0.001204   2.349521  0.018798
-3  log_sunny_hours      0.18476  0.036508   5.060818       0.0
-4           lambda     0.840532   0.01232  68.225574       0.0</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     7.072171  0.526531  13.431638       0.0
-1         adensity    -0.000041  0.000029  -1.416209  0.156865
-2       log_income    -1.245718  0.078663 -15.836081       0.0
-3       log_hholds     0.006102  0.009166   0.665681  0.505689
-4  log_sunny_hours     0.432934  0.165408   2.617373  0.008925</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     7.072171  0.526531  13.431638       0.0
-1         adensity    -0.000041  0.000029  -1.416209  0.156865
-2       log_income    -1.245718  0.078663 -15.836081       0.0
-3       log_hholds     0.006102  0.009166   0.665681  0.505689
-4  log_sunny_hours     0.432934  0.165408   2.617373  0.008925</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     7.072171  0.526531  13.431638       0.0
-1         adensity    -0.000041  0.000029  -1.416209  0.156865
-2       log_income    -1.245718  0.078663 -15.836081       0.0
-3       log_hholds     0.006102  0.009166   0.665681  0.505689
-4  log_sunny_hours     0.432934  0.165408   2.617373  0.008925</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT    -4.704719  0.203307 -23.140973       0.0
-1         adensity     0.000002  0.000004   0.607713  0.543378
-2       log_income     1.958665  0.042498  46.088349       0.0
-3       log_hholds     0.000197  0.002215   0.088743  0.929286
-4  log_sunny_hours    -0.169635  0.043301  -3.917602  0.000089</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT    -4.704719  0.203307 -23.140973       0.0
-1         adensity     0.000002  0.000004   0.607713  0.543378
-2       log_income     1.958665  0.042498  46.088349       0.0
-3       log_hholds     0.000197  0.002215   0.088743  0.929286
-4  log_sunny_hours    -0.169635  0.043301  -3.917602  0.000089</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT    -4.704719  0.203307 -23.140973       0.0
-1         adensity     0.000002  0.000004   0.607713  0.543378
-2       log_income     1.958665  0.042498  46.088349       0.0
-3       log_hholds     0.000197  0.002215   0.088743  0.929286
-4  log_sunny_hours    -0.169635  0.043301  -3.917602  0.000089</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>effects</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE(SLX)_inverse_distance  \
-adensity                                    -0.000494   
-log_income                                   3.961491   
-log_hholds                                  -0.453237   
-log_sunny_hours                             -0.993670   
-                 direct_ML_LagFE(SLX)_inverse_distance  \
-adensity                                      0.000005   
-log_income                                   -0.061540   
-log_hholds                                    0.000808   
-log_sunny_hours                               0.161963   
-                 indirect_ML_LagFE(SLX)_inverse_distance  
-adensity                                       -0.000499  
-log_income                                      4.023031  
-log_hholds                                     -0.454044  
-log_sunny_hours                                -1.155632  </t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE(SLX)_k_nearest  \
-adensity                             -0.000034   
-log_income                            2.481649   
-log_hholds                           -0.028276   
-log_sunny_hours                      -0.614053   
-                 direct_ML_LagFE(SLX)_k_nearest  \
-adensity                               0.000004   
-log_income                             0.000206   
-log_hholds                             0.001038   
-log_sunny_hours                        0.146110   
-                 indirect_ML_LagFE(SLX)_k_nearest  
-adensity                                -0.000039  
-log_income                               2.481443  
-log_hholds                              -0.029314  
-log_sunny_hours                         -0.760163  </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE(SLX)_queen  direct_ML_LagFE(SLX)_queen  \
-adensity                         -0.000012                    0.000004   
-log_income                        2.385965                    0.035692   
-log_hholds                       -0.018023                    0.001132   
-log_sunny_hours                  -0.517048                    0.111162   
-                 indirect_ML_LagFE(SLX)_queen  
-adensity                            -0.000016  
-log_income                           2.350273  
-log_hholds                          -0.019155  
-log_sunny_hours                     -0.628210  </t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE_inverse_distance  \
-adensity                                0.000123   
-log_income                              0.866638   
-log_hholds                              0.026070   
-log_sunny_hours                         1.778769   
-                 direct_ML_LagFE_inverse_distance  \
-adensity                                 0.000005   
-log_income                               0.033044   
-log_hholds                               0.000994   
-log_sunny_hours                          0.067822   
-                 indirect_ML_LagFE_inverse_distance  
-adensity                                   0.000118  
-log_income                                 0.833594  
-log_hholds                                 0.025076  
-log_sunny_hours                            1.710947  </t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE_k_nearest  direct_ML_LagFE_k_nearest  \
-adensity                         0.000020                   0.000004   
-log_income                       1.909008                   0.410693   
-log_hholds                       0.007350                   0.001581   
-log_sunny_hours                  0.103365                   0.022237   
-                 indirect_ML_LagFE_k_nearest  
-adensity                            0.000016  
-log_income                          1.498315  
-log_hholds                          0.005769  
-log_sunny_hours                     0.081128  </t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE_queen  direct_ML_LagFE_queen  \
-adensity                     0.000013               0.000004   
-log_income                   1.967993               0.607145   
-log_hholds                   0.005460               0.001684   
-log_sunny_hours              0.005164               0.001593   
-                 indirect_ML_LagFE_queen  
-adensity                        0.000009  
-log_income                      1.360847  
-log_hholds                      0.003776  
-log_sunny_hours                 0.003571  </t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>lambda</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>0.973***</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>0.891***</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>0.841***</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>CONSTANT</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>7.072***</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>7.072***</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>7.072***</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>-4.705***</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>-4.705***</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>-4.705***</t>
+          <t>N obs.</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2076</t>
         </is>
       </c>
     </row>
